--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260806.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.50%</t>
+          <t>9.28%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.31%</t>
+          <t>8.34%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.10%</t>
+          <t>6.90%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>6.36%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.55%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,708,000</t>
+          <t>5,801,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.51%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,801,000</t>
+          <t>2,708,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>5.49%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>5.00%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>4.98%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>4.69%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>87,718,000</t>
+          <t>6,505,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>17,439,000</t>
+          <t>87,718,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
@@ -924,29 +924,29 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,932,000</t>
+          <t>17,439,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>5,556,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1029,56 +1029,56 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,957,000</t>
+          <t>2,053,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,295,450</t>
+          <t>2,497,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,297,000</t>
+          <t>11,295,450</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1100,24 +1100,24 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,874,000</t>
+          <t>472,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,39 +1129,39 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>472,000</t>
+          <t>1,874,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,682,000</t>
+          <t>528,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>528,000</t>
+          <t>712,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>712,000</t>
+          <t>1,682,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1232,68 +1232,68 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>3,250,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>3,250,000</t>
+          <t>2,224,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>2,224,000</t>
+          <t>940,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,44 +1305,44 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>940,000</t>
+          <t>1,080,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,080,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1393,22 +1393,22 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>33,245,921,768</t>
+          <t>26,086,970,077</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,496,768,006</t>
+          <t>4,388,516,006</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>-6,390,743,003</t>
+          <t>48,814,018</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
